--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/MAINE_2021.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/MAINE_2021.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C2">
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -465,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C8">
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -504,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -550,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -581,12 +631,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C16">
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -617,7 +672,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C18">
@@ -628,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -661,7 +726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C21">
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Tlacoapa</t>
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -742,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
@@ -786,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -799,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -830,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -861,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -874,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Xiutetelco</t>
@@ -887,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -918,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -931,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Total</t>
@@ -962,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Total</t>
@@ -993,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1016,41 +1161,6 @@
       </c>
       <c r="D45">
         <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 701,861</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Mayo de 2022</t>
-        </is>
       </c>
     </row>
   </sheetData>
